--- a/artifacts/reports/architecture_tuning_logistic_v1.xlsx
+++ b/artifacts/reports/architecture_tuning_logistic_v1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05677440301952207</v>
+        <v>0.05858914021776086</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23.58183327221519</v>
+        <v>23.93232768333433</v>
       </c>
     </row>
     <row r="16">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.28351405012654</v>
+        <v>18.02378265000152</v>
       </c>
     </row>
     <row r="17">
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,105 +921,115 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>num_layers</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dropout</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>train_r</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>r_min</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>r_max</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>hidden_dims</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>params_json</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>params_repr</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>n_series</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>horizon</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>mae_mean</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>rmse_mean</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>mase_mean</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>directional_accuracy_mean</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fit_time_sec_mean</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>predict_time_sec_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>fit_time</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>predict_time</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>total_runtime_sec</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1028,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,80 +1067,82 @@
       <c r="M2" t="n">
         <v>32</v>
       </c>
-      <c r="N2" t="b">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>3.95</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs32", "model_params": {"beta": 0.2, "hidden_size": 32, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 32, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs32'}</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>12</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>1</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.09591769381652354</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.09919956525440514</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>10.64925032965593</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.4879651319202673</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0.659988936095033</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.007995727785681892</v>
-      </c>
       <c r="AD2" t="n">
-        <v>0.659988936095033</v>
+        <v>0.6732829166673279</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.007995727785681892</v>
+        <v>0.008192263888405353</v>
       </c>
       <c r="AF2" t="n">
-        <v>24.04744789970573</v>
-      </c>
-      <c r="AG2" t="inlineStr">
+        <v>0.6732829166673279</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.008192263888405353</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>24.5331065000064</v>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1159,80 +1171,82 @@
       <c r="M3" t="n">
         <v>32</v>
       </c>
-      <c r="N3" t="b">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="b">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.2</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>3.95</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs32", "model_params": {"beta": 0.2, "hidden_size": 32, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 32, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs32'}</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>12</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>5</v>
       </c>
-      <c r="X3" t="n">
-        <v>0.1016502611474948</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.1087691505696343</v>
-      </c>
       <c r="Z3" t="n">
-        <v>11.19747114055942</v>
+        <v>0.1055578440898528</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5060429831528576</v>
+        <v>0.1126118602442209</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3543836694475935</v>
+        <v>11.637080603625</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.004158952781128593</v>
+        <v>0.5076444447952301</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3543836694475935</v>
+        <v>0.352510058334398</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004158952781128593</v>
+        <v>0.004404383332358622</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.907534400234</v>
-      </c>
-      <c r="AG3" t="inlineStr">
+        <v>0.352510058334398</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.004404383332358622</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>12.84891990000324</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1261,80 +1275,82 @@
       <c r="M4" t="n">
         <v>32</v>
       </c>
-      <c r="N4" t="b">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="b">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.2</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>3.95</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs32", "model_params": {"beta": 0.2, "hidden_size": 32, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 32, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs32'}</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>12</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>20</v>
       </c>
-      <c r="X4" t="n">
-        <v>0.1206168158783188</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.1328177505252469</v>
-      </c>
       <c r="Z4" t="n">
-        <v>12.2021721670235</v>
+        <v>0.1345907684324672</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.512065276863073</v>
+        <v>0.1465116672390476</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2291454861244549</v>
+        <v>13.89491231432359</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002308547218692386</v>
+        <v>0.503866136283331</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2291454861244549</v>
+        <v>0.2231346777783376</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002308547218692386</v>
+        <v>0.002368200000799131</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.332345200353302</v>
-      </c>
-      <c r="AG4" t="inlineStr">
+        <v>0.2231346777783376</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.002368200000799131</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>8.118103600048926</v>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1363,80 +1379,82 @@
       <c r="M5" t="n">
         <v>64</v>
       </c>
-      <c r="N5" t="b">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="b">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.2</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>3.95</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs64", "model_params": {"beta": 0.2, "hidden_size": 64, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs64'}</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>12</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>1</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.01558467145045791</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>0.01932025859289997</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>1.328977194925385</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.4886821623660602</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0.6720405861107995</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.01015583334244891</v>
-      </c>
       <c r="AD5" t="n">
-        <v>0.6720405861107995</v>
+        <v>0.6895206194458297</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01015583334244891</v>
+        <v>0.01221793055447051</v>
       </c>
       <c r="AF5" t="n">
-        <v>24.55907110031694</v>
-      </c>
-      <c r="AG5" t="inlineStr">
+        <v>0.6895206194458297</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.01221793055447051</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25.26258780001081</v>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1465,80 +1483,82 @@
       <c r="M6" t="n">
         <v>64</v>
       </c>
-      <c r="N6" t="b">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="b">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.2</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>3.95</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs64", "model_params": {"beta": 0.2, "hidden_size": 64, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs64'}</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>12</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>5</v>
       </c>
-      <c r="X6" t="n">
-        <v>0.02732685919862286</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.03536172942424668</v>
-      </c>
       <c r="Z6" t="n">
-        <v>2.119013119401744</v>
+        <v>0.02725666118610368</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5014039261620158</v>
+        <v>0.03528170784519475</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4028926972176931</v>
+        <v>2.11779019889337</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.005171983331416009</v>
+        <v>0.4915809352615879</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4028926972176931</v>
+        <v>0.4048224583340116</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.005171983331416009</v>
+        <v>0.005806322222472065</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.69032849976793</v>
-      </c>
-      <c r="AG6" t="inlineStr">
+        <v>0.4048224583340116</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.005806322222472065</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14.78263610003341</v>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1567,80 +1587,82 @@
       <c r="M7" t="n">
         <v>64</v>
       </c>
-      <c r="N7" t="b">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="b">
         <v>0</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.2</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>3.95</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs64", "model_params": {"beta": 0.2, "hidden_size": 64, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs64'}</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>12</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>20</v>
       </c>
-      <c r="X7" t="n">
-        <v>0.05255246376432737</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.06578746885732568</v>
-      </c>
       <c r="Z7" t="n">
-        <v>3.630146968176863</v>
+        <v>0.05158785520102299</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4926974765658623</v>
+        <v>0.06470709328472882</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2487480388889607</v>
+        <v>3.524975834574505</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.002857038899997456</v>
+        <v>0.5136159892963549</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2487480388889607</v>
+        <v>0.2338595722232842</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002857038899997456</v>
+        <v>0.003089847222630245</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.057782800402492</v>
-      </c>
-      <c r="AG7" t="inlineStr">
+        <v>0.2338595722232842</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.003089847222630245</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8.530179100052919</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1669,80 +1691,82 @@
       <c r="M8" t="n">
         <v>128</v>
       </c>
-      <c r="N8" t="b">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="b">
         <v>0</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.2</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>3.95</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>[128]</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs128", "model_params": {"beta": 0.2, "hidden_size": 128, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 128, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs128'}</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>12</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>1</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.01915814620150542</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.02267586612114576</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>1.607654121520208</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.489009921511558</v>
       </c>
-      <c r="AB8" t="n">
-        <v>0.8618076083269748</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.01215247498799322</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0.8618076083269748</v>
+        <v>0.8897681694434142</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01215247498799322</v>
+        <v>0.01318041388933327</v>
       </c>
       <c r="AF8" t="n">
-        <v>31.46256299933884</v>
-      </c>
-      <c r="AG8" t="inlineStr">
+        <v>0.8897681694434142</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.01318041388933327</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>32.5061489999789</v>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1771,80 +1795,82 @@
       <c r="M9" t="n">
         <v>128</v>
       </c>
-      <c r="N9" t="b">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="b">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.2</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>3.95</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>[128]</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs128", "model_params": {"beta": 0.2, "hidden_size": 128, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 128, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs128'}</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>12</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>5</v>
       </c>
-      <c r="X9" t="n">
-        <v>0.02841954246215345</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.03630862651155959</v>
-      </c>
       <c r="Z9" t="n">
-        <v>2.13167236950887</v>
+        <v>0.02834192226388195</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5206362910487875</v>
+        <v>0.0361792354038653</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4915881527898212</v>
+        <v>2.123905349150364</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.006772213880645319</v>
+        <v>0.5241163648869064</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.4915881527898212</v>
+        <v>0.4988307722228962</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.006772213880645319</v>
+        <v>0.007142086110333265</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.9409732001368</v>
-      </c>
-      <c r="AG9" t="inlineStr">
+        <v>0.4988307722228962</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.007142086110333265</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18.21502289999626</v>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1873,80 +1899,82 @@
       <c r="M10" t="n">
         <v>128</v>
       </c>
-      <c r="N10" t="b">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="b">
         <v>0</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.2</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>3.95</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>[128]</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs128", "model_params": {"beta": 0.2, "hidden_size": 128, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 128, 'train_r': False, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs128'}</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>12</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>20</v>
       </c>
-      <c r="X10" t="n">
-        <v>0.05209968998063932</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.06535243625507363</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.299124511543681</v>
+        <v>0.05256624141715788</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5278509291241463</v>
+        <v>0.06566990255437345</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.3007114749925676</v>
+        <v>3.342157649873342</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.003553163900505751</v>
+        <v>0.5264681131281784</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3007114749925676</v>
+        <v>0.2963492194438812</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.003553163900505751</v>
+        <v>0.003613725001842896</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.95352700015064</v>
-      </c>
-      <c r="AG10" t="inlineStr">
+        <v>0.2963492194438812</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.003613725001842896</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>10.79866600004607</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1975,80 +2003,82 @@
       <c r="M11" t="n">
         <v>32</v>
       </c>
-      <c r="N11" t="b">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="b">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.2</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>3.95</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs32", "model_params": {"beta": 0.2, "hidden_size": 32, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": true}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 32, 'train_r': True, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs32'}</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>12</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>1</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.09577202009296559</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>0.09905366047432657</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AB11" t="n">
         <v>10.63408404706972</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>0.4880053313092366</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.605294263895808</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.007860024996464036</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.605294263895808</v>
+        <v>1.644564311108196</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.007860024996464036</v>
+        <v>0.008322736112151891</v>
       </c>
       <c r="AF11" t="n">
-        <v>58.07355440012179</v>
-      </c>
-      <c r="AG11" t="inlineStr">
+        <v>1.644564311108196</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.008322736112151891</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>59.50393369993253</v>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2077,80 +2107,82 @@
       <c r="M12" t="n">
         <v>32</v>
       </c>
-      <c r="N12" t="b">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="b">
         <v>1</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.2</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>3.95</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs32", "model_params": {"beta": 0.2, "hidden_size": 32, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": true}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 32, 'train_r': True, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs32'}</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>12</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>5</v>
       </c>
-      <c r="X12" t="n">
-        <v>0.1015054903620158</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.1086259552008296</v>
-      </c>
       <c r="Z12" t="n">
-        <v>11.18209299031321</v>
+        <v>0.1053914836552426</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5000654866690321</v>
+        <v>0.1124574038575065</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8213256305445814</v>
+        <v>11.62003627070016</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.004007777774758223</v>
+        <v>0.5082337894439807</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.8213256305445814</v>
+        <v>0.8334354722214306</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.004007777774758223</v>
+        <v>0.004397769444444242</v>
       </c>
       <c r="AF12" t="n">
-        <v>29.71200269949622</v>
-      </c>
-      <c r="AG12" t="inlineStr">
+        <v>0.8334354722214306</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.004397769444444242</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>30.1619966999715</v>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2179,80 +2211,82 @@
       <c r="M13" t="n">
         <v>32</v>
       </c>
-      <c r="N13" t="b">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="b">
         <v>1</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.2</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>3.95</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>[32]</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs32", "model_params": {"beta": 0.2, "hidden_size": 32, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": true}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 32, 'train_r': True, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs32'}</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>12</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>20</v>
       </c>
-      <c r="X13" t="n">
-        <v>0.1204229316137702</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.1326379727348315</v>
-      </c>
       <c r="Z13" t="n">
-        <v>12.18307179256713</v>
+        <v>0.1343822209822163</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.512065276863073</v>
+        <v>0.1463182351035207</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.4629500305551724</v>
+        <v>13.87469743655049</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.002084469438866816</v>
+        <v>0.5046552776974724</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.4629500305551724</v>
+        <v>0.4591897027781265</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.002084469438866816</v>
+        <v>0.002218555556788084</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.74124199978542</v>
-      </c>
-      <c r="AG13" t="inlineStr">
+        <v>0.4591897027781265</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.002218555556788084</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>16.61069730005693</v>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2281,80 +2315,82 @@
       <c r="M14" t="n">
         <v>64</v>
       </c>
-      <c r="N14" t="b">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="b">
         <v>1</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.2</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>3.95</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs64", "model_params": {"beta": 0.2, "hidden_size": 64, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": true}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': True, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs64'}</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>12</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>1</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.01563299792962186</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.01935923589810141</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>1.331559005014425</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.4886821623660602</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.769108780546554</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.01001484723140796</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.769108780546554</v>
+        <v>1.818762874999973</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01001484723140796</v>
+        <v>0.01091903055526523</v>
       </c>
       <c r="AF14" t="n">
-        <v>64.04845060000662</v>
-      </c>
-      <c r="AG14" t="inlineStr">
+        <v>1.818762874999973</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.01091903055526523</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>65.86854859998857</v>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2383,80 +2419,82 @@
       <c r="M15" t="n">
         <v>64</v>
       </c>
-      <c r="N15" t="b">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="b">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.2</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>3.95</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs64", "model_params": {"beta": 0.2, "hidden_size": 64, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": true}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': True, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs64'}</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>12</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>5</v>
       </c>
-      <c r="X15" t="n">
-        <v>0.02732718307242137</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.03536031505681476</v>
-      </c>
       <c r="Z15" t="n">
-        <v>2.116904060327776</v>
+        <v>0.02725915391794867</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.5014039261620158</v>
+        <v>0.0352813812768367</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9668680833290435</v>
+        <v>2.115736742278405</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.005145163886481896</v>
+        <v>0.4915809352615879</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.9668680833290435</v>
+        <v>0.9799336333336317</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.005145163886481896</v>
+        <v>0.005442327779342628</v>
       </c>
       <c r="AF15" t="n">
-        <v>34.99247689975891</v>
-      </c>
-      <c r="AG15" t="inlineStr">
+        <v>0.9799336333336317</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.005442327779342628</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>35.47353460006707</v>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2485,80 +2523,82 @@
       <c r="M16" t="n">
         <v>64</v>
       </c>
-      <c r="N16" t="b">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="b">
         <v>1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.2</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>3.95</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_hs64", "model_params": {"beta": 0.2, "hidden_size": 64, "r_max": 3.95, "r_min": 3.65, "seed": 2026, "train_r": true}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': True, 'beta': 0.2, 'r_min': 3.65, 'r_max': 3.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_hs64'}</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>12</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>20</v>
       </c>
-      <c r="X16" t="n">
-        <v>0.05254473461127824</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.06577958103159781</v>
-      </c>
       <c r="Z16" t="n">
-        <v>3.629346391026968</v>
+        <v>0.05157193835593701</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.4926974765658623</v>
+        <v>0.06468422155873073</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.5147254722251091</v>
+        <v>3.52324770737514</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.002664941667009973</v>
+        <v>0.5136159892963549</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5147254722251091</v>
+        <v>0.4923924055559231</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.002664941667009973</v>
+        <v>0.002955994444265444</v>
       </c>
       <c r="AF16" t="n">
-        <v>18.62605490011629</v>
-      </c>
-      <c r="AG16" t="inlineStr">
+        <v>0.4923924055559231</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.002955994444265444</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>17.83254240000679</v>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2587,80 +2627,82 @@
       <c r="M17" t="n">
         <v>64</v>
       </c>
-      <c r="N17" t="b">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="b">
         <v>0</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.08</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>3.55</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>3.8</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_alt64", "model_params": {"beta": 0.08, "hidden_size": 64, "r_max": 3.8, "r_min": 3.55, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': False, 'beta': 0.08, 'r_min': 3.55, 'r_max': 3.8, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_alt64'}</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>12</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>1</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>0.01551204458428915</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>0.01924901909655832</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>1.319655196679135</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.4886821623660602</v>
       </c>
-      <c r="AB17" t="n">
-        <v>0.6725408638853372</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.0101126111112535</v>
-      </c>
       <c r="AD17" t="n">
-        <v>0.6725408638853372</v>
+        <v>0.7040682527763744</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0101126111112535</v>
+        <v>0.01098427499972685</v>
       </c>
       <c r="AF17" t="n">
-        <v>24.57552509987727</v>
-      </c>
-      <c r="AG17" t="inlineStr">
+        <v>0.7040682527763744</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.01098427499972685</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25.74189099993964</v>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2689,80 +2731,82 @@
       <c r="M18" t="n">
         <v>64</v>
       </c>
-      <c r="N18" t="b">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="b">
         <v>0</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.08</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>3.55</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>3.8</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_alt64", "model_params": {"beta": 0.08, "hidden_size": 64, "r_max": 3.8, "r_min": 3.55, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': False, 'beta': 0.08, 'r_min': 3.55, 'r_max': 3.8, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_alt64'}</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>12</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>5</v>
       </c>
-      <c r="X18" t="n">
-        <v>0.02725152715350347</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.03528467251065843</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.108902412868351</v>
+        <v>0.02717554931306084</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.5014039261620158</v>
+        <v>0.0352008760312636</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.4038229527747414</v>
+        <v>2.107163628893262</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.005392308340459648</v>
+        <v>0.4915809352615879</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.4038229527747414</v>
+        <v>0.4170978833321391</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.005392308340459648</v>
+        <v>0.005770405555166588</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.73174940014724</v>
-      </c>
-      <c r="AG18" t="inlineStr">
+        <v>0.4170978833321391</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.005770405555166588</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>15.22325839994301</v>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2791,75 +2835,77 @@
       <c r="M19" t="n">
         <v>64</v>
       </c>
-      <c r="N19" t="b">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="b">
         <v>0</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.08</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>3.55</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>3.8</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>[64]</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>{"compare_group_id": "logistic_alt64", "model_params": {"beta": 0.08, "hidden_size": 64, "r_max": 3.8, "r_min": 3.55, "seed": 2026, "train_r": false}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>{'model_params': {'hidden_size': 64, 'train_r': False, 'beta': 0.08, 'r_min': 3.55, 'r_max': 3.8, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'logistic_alt64'}</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>12</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>20</v>
       </c>
-      <c r="X19" t="n">
-        <v>0.0526441810314881</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.06589063293466783</v>
-      </c>
       <c r="Z19" t="n">
-        <v>3.648505865533874</v>
+        <v>0.05134531102943998</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.4926974765658623</v>
+        <v>0.06448364610556183</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.2477264750082718</v>
+        <v>3.503918426516095</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.00283935277386465</v>
+        <v>0.5136159892963549</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2477264750082718</v>
+        <v>0.2404493027772534</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.00283935277386465</v>
+        <v>0.003165272220940096</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.020369800156914</v>
-      </c>
-      <c r="AG19" t="inlineStr">
+        <v>0.2404493027772534</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.003165272220940096</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>8.770124699934968</v>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2954,10 +3000,10 @@
         <v>0.4886821623660602</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6725408638853372</v>
+        <v>0.7040682527763744</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0101126111112535</v>
+        <v>0.01098427499972685</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2980,22 +3026,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02725152715350347</v>
+        <v>0.02717554931306084</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03528467251065843</v>
+        <v>0.0352008760312636</v>
       </c>
       <c r="F3" t="n">
-        <v>2.108902412868351</v>
+        <v>2.107163628893262</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5014039261620158</v>
+        <v>0.4915809352615879</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4038229527747414</v>
+        <v>0.4170978833321391</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005392308340459648</v>
+        <v>0.005770405555166588</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3014,26 +3060,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>logistic_g003</t>
+          <t>logistic_g006</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05209968998063932</v>
+        <v>0.05134531102943998</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06535243625507363</v>
+        <v>0.06448364610556183</v>
       </c>
       <c r="F4" t="n">
-        <v>3.299124511543681</v>
+        <v>3.503918426516095</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5278509291241463</v>
+        <v>0.5136159892963549</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3007114749925676</v>
+        <v>0.2404493027772534</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003553163900505751</v>
+        <v>0.003165272220940096</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3052,7 +3098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3073,80 +3119,175 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>base_model_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>chaotic_model_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>secondary_model_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>base_candidate_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>chaotic_candidate_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>secondary_candidate_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>base_mae_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>chaotic_mae_mean</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>secondary_mae_mean</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>chaotic_delta_mae_vs_base</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>secondary_delta_mae_vs_base</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>base_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>chaotic_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>secondary_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>chaotic_runtime_delta_sec_vs_base</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>secondary_runtime_delta_sec_vs_base</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>base_status</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>chaotic_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>secondary_status</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>esn_candidate_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>chaotic_esn_candidate_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_candidate_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>esn_mae_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>chaotic_esn_mae_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_mae_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>chaotic_esn_delta_mae_vs_esn</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_delta_mae_vs_esn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>chaotic_esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>chaotic_esn_runtime_delta_sec_vs_esn</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_runtime_delta_sec_vs_esn</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>esn_status</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>chaotic_esn_status</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_status</t>
         </is>
@@ -3231,7 +3372,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3245,25 +3386,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03180258425642691</v>
+        <v>0.03134430164226332</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04014144151396153</v>
+        <v>0.03964451374446125</v>
       </c>
       <c r="F2" t="n">
-        <v>2.359021158360453</v>
+        <v>2.310245750696164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4942611883646461</v>
+        <v>0.4979596956413343</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4413634305561168</v>
+        <v>0.4538718129619223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006114757408525931</v>
+        <v>0.006639984258611178</v>
       </c>
       <c r="J2" t="n">
-        <v>16.10921476672714</v>
+        <v>16.57842469993921</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3310,7 +3451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_logistic_v1_20260329T164249Z</t>
+          <t>architecture_tuning_logistic_v1_20260819T071234Z</t>
         </is>
       </c>
     </row>
